--- a/Project-5-AdventureWorks-Sales-Performance-Analysis/excel/03_WhatIf_Simulation/03_WhatIf.xlsx
+++ b/Project-5-AdventureWorks-Sales-Performance-Analysis/excel/03_WhatIf_Simulation/03_WhatIf.xlsx
@@ -5,12 +5,14 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="WhatIf_Baseline" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="WhatIf_Input" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="WhatIf_Calculation" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Summary_WhatIf" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="WhatIf_Baseline" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="WhatIf_Input" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="WhatIf_Calculation" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="WhatIf_Viz" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -22,7 +24,367 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="92">
+  <si>
+    <t xml:space="preserve">What-If Simulation: Profit Recovery 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asumsi Dasar:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Bikes margin improvement: 1%, 5%, 10%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Pacific returns reduction: 10%, 20%, 30%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Non-Bikes volume growth: 10% (konservatif)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hasil Simulasi:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margin Bikes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Returns Pacific</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profit 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VS 2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VS 2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skenario 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-10%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✅ Kembali ke 2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skenario 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-20%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+4.4% di atas 2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skenario 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+10%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-30%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+9.9% di atas 2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insight Utama:</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Skenario 1 sudah cukup</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> untuk mengembalikan profit ke level 2021.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">- Hanya butuh margin Bikes naik 1% + returns Pacific turun 10%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Sangat realistis dalam 1 tahun.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Skenario 2 (paling direkomendasikan)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">- Margin +5% (target achievable dengan audit Road-250).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Returns -20% (quality control Pacific).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Profit naik 6.72% → 3,854,486.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Skenario 3 terlalu agresif</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (butuh margin +10% + returns -30%).</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Rekomendasi Final:</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Short-term (Q1-Q2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: Fokus pada </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Road-250</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (penyebab utama). Target margin +5%.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Medium-term (Q3-Q4)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: Kurangi returns Pacific 20% via quality control.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Target 2023</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: Profit minimal </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.69 juta</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (kembali ke 2021), optimis </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.85 juta</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (+6.7%).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Catatan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: Tidak perlu perubahan besar. Perbaikan kecil sudah berdampak signifikan.</t>
+    </r>
+  </si>
   <si>
     <t xml:space="preserve">Item</t>
   </si>
@@ -120,15 +482,6 @@
     <t xml:space="preserve">Component</t>
   </si>
   <si>
-    <t xml:space="preserve">Skenario 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skenario 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skenario 3</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bikes Impact</t>
   </si>
   <si>
@@ -168,7 +521,7 @@
     <t xml:space="preserve">Volume Growth %</t>
   </si>
   <si>
-    <t xml:space="preserve">New Profit from</t>
+    <t xml:space="preserve">New Profit from volume</t>
   </si>
   <si>
     <t xml:space="preserve">Volume Gain</t>
@@ -190,20 +543,24 @@
   </si>
   <si>
     <t xml:space="preserve">Improvement %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profit 2022 (Baseline)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0.00"/>
-    <numFmt numFmtId="166" formatCode="0"/>
-    <numFmt numFmtId="167" formatCode="0%"/>
-    <numFmt numFmtId="168" formatCode="0.00%"/>
+    <numFmt numFmtId="165" formatCode="@"/>
+    <numFmt numFmtId="166" formatCode="0.00"/>
+    <numFmt numFmtId="167" formatCode="0.00%"/>
+    <numFmt numFmtId="168" formatCode="0"/>
+    <numFmt numFmtId="169" formatCode="0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -227,7 +584,14 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="12"/>
+      <sz val="15"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -240,11 +604,28 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -364,24 +745,108 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="48">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -389,27 +854,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -417,27 +882,23 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -457,15 +918,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -494,7 +963,7 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FFB3B3B3"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
@@ -524,11 +993,11 @@
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF8000"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF004586"/>
       <rgbColor rgb="FF00A933"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
@@ -539,6 +1008,562 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:rPr>
+              <a:t>Profit Recovery 2023 – 3 Skenario</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.189900978286805"/>
+          <c:y val="0.126909413854352"/>
+          <c:w val="0.4794201861131"/>
+          <c:h val="0.741918294849023"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>WhatIf_Viz!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total Profit 2023</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="004586"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="ff8000"/>
+              </a:solidFill>
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="ffff00"/>
+              </a:solidFill>
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="00a933"/>
+              </a:solidFill>
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:txPr>
+                <a:bodyPr wrap="none"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                      <a:uFillTx/>
+                      <a:latin typeface="Arial"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:separator> </c:separator>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:txPr>
+                <a:bodyPr wrap="none"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                      <a:uFillTx/>
+                      <a:latin typeface="Arial"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:separator> </c:separator>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:txPr>
+                <a:bodyPr wrap="none"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                      <a:uFillTx/>
+                      <a:latin typeface="Arial"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:separator> </c:separator>
+            </c:dLbl>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>WhatIf_Viz!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Skenario 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Skenario 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Skenario 3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>WhatIf_Viz!$B$2:$D$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>3690735</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3854486.3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4056093.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="100"/>
+        <c:overlap val="0"/>
+        <c:axId val="73944381"/>
+        <c:axId val="24552368"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>WhatIf_Viz!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Profit 2022 (Baseline)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ff0000"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="ff0000"/>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="28800">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:prstDash val="sysDash"/>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>WhatIf_Viz!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Skenario 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Skenario 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Skenario 3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>WhatIf_Viz!$B$3:$D$3</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>3611731</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3611731</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3611731</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="0"/>
+        <c:axId val="73944381"/>
+        <c:axId val="24552368"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="73944381"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="24552368"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="24552368"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="b3b3b3"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr sz="900" b="1" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:rPr>
+                  <a:t>Total Profit</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="73944381"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="b3b3b3"/>
+          </a:solidFill>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="0">
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>141840</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>77040</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>487440</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>66600</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="1" name=""/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="4193280" y="267480"/>
+        <a:ext cx="6035040" cy="4053600"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -652,150 +1677,206 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23.55"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="44.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="60.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="12.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="17.29"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="6" t="n">
-        <v>3611731</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="6" t="n">
-        <v>3477544</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>3647021</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6" t="n">
-        <v>255681</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="F8" s="8" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="G8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="6" t="n">
-        <v>782523</v>
-      </c>
-      <c r="C6" s="5" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="C9" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>1366646</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="D9" s="11" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="E9" s="12" t="n">
+        <f aca="false">WhatIf_Calculation!B21</f>
+        <v>3690735</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <f aca="false">WhatIf_Calculation!B23</f>
+        <v>0.0218742757973948</v>
+      </c>
+      <c r="G9" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="6" t="n">
-        <v>1570398</v>
-      </c>
-      <c r="C8" s="5" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="C10" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="6" t="n">
-        <v>277297</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+      <c r="D10" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="6" t="n">
-        <v>1944835</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="E10" s="14" t="n">
+        <f aca="false">WhatIf_Calculation!C21</f>
+        <v>3854486.3</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <f aca="false">WhatIf_Calculation!C23</f>
+        <v>0.0672130067272453</v>
+      </c>
+      <c r="G10" s="11" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="7" t="n">
-        <v>972</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
+      <c r="C11" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>4</v>
+      <c r="D11" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <f aca="false">WhatIf_Calculation!D21</f>
+        <v>4056093.2</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <f aca="false">WhatIf_Calculation!D23</f>
+        <v>0.123033027653499</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="21" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -808,86 +1889,150 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="22" width="23.55"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="23" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="22" width="44.98"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>26</v>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="11" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D2" s="11" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E2" s="11" t="n">
-        <v>0.1</v>
+      <c r="A2" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="27" t="n">
+        <v>3611731</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="11" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="D3" s="11" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="E3" s="11" t="n">
-        <v>-0.3</v>
+      <c r="A3" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="27" t="n">
+        <v>3477544</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>0.1</v>
+      <c r="A4" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="27" t="n">
+        <v>3647021</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="27" t="n">
+        <v>255681</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="27" t="n">
+        <v>782523</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="27" t="n">
+        <v>1366646</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="27" t="n">
+        <v>1570398</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="27" t="n">
+        <v>277297</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="27" t="n">
+        <v>1944835</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="28" t="n">
+        <v>972</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -900,364 +2045,454 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="22" width="23.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="22" width="16.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="22" width="11.85"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="31" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="32" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D2" s="32" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E2" s="32" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="32" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="D3" s="32" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E3" s="32" t="n">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D4" s="30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E4" s="30" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:D23"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="12.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="22" width="22.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="22" width="12.84"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>34</v>
+      <c r="A1" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
+      <c r="A2" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="14" t="n">
+      <c r="A3" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="35" t="n">
         <f aca="false">WhatIf_Baseline!$B$3</f>
         <v>3477544</v>
       </c>
-      <c r="C3" s="14" t="n">
+      <c r="C3" s="35" t="n">
         <f aca="false">WhatIf_Baseline!$B$3</f>
         <v>3477544</v>
       </c>
-      <c r="D3" s="14" t="n">
+      <c r="D3" s="35" t="n">
         <f aca="false">WhatIf_Baseline!$B$3</f>
         <v>3477544</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="15" t="n">
-        <f aca="false">WhatIf_Input!C$2</f>
-        <v>0.02</v>
-      </c>
-      <c r="C4" s="15" t="n">
-        <f aca="false">WhatIf_Input!D$2</f>
+      <c r="A4" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="36" t="n">
+        <v>0.0108857285486538</v>
+      </c>
+      <c r="C4" s="36" t="n">
         <v>0.05</v>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="36" t="n">
         <f aca="false">WhatIf_Input!E$2</f>
         <v>0.1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="5" t="n">
+      <c r="A5" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="26" t="n">
         <f aca="false">B3*(1+B4)</f>
-        <v>3547094.88</v>
-      </c>
-      <c r="C5" s="5" t="n">
+        <v>3515399.6</v>
+      </c>
+      <c r="C5" s="26" t="n">
         <f aca="false">C3*(1+C4)</f>
         <v>3651421.2</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="26" t="n">
         <f aca="false">D3*(1+D4)</f>
         <v>3825298.4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="8" t="n">
+      <c r="A6" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="29" t="n">
         <f aca="false">B5-B3</f>
-        <v>69550.8799999999</v>
-      </c>
-      <c r="C6" s="8" t="n">
+        <v>37855.6000000001</v>
+      </c>
+      <c r="C6" s="29" t="n">
         <f aca="false">C5-C3</f>
         <v>173877.2</v>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="29" t="n">
         <f aca="false">D5-D3</f>
         <v>347754.4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
+      <c r="A7" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="16" t="n">
+      <c r="A8" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="37" t="n">
         <f aca="false">WhatIf_Baseline!$B$9</f>
         <v>277297</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="37" t="n">
         <f aca="false">WhatIf_Baseline!$B$9</f>
         <v>277297</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="35" t="n">
         <f aca="false">WhatIf_Baseline!$B$9</f>
         <v>277297</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="18" t="n">
+      <c r="A9" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="38" t="n">
         <f aca="false">WhatIf_Input!C$3</f>
         <v>-0.1</v>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="32" t="n">
         <f aca="false">WhatIf_Input!D$3</f>
         <v>-0.2</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="32" t="n">
         <f aca="false">WhatIf_Input!E$3</f>
         <v>-0.3</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="19" t="n">
+      <c r="A10" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="39" t="n">
         <f aca="false">B8*(1+B9)</f>
         <v>249567.3</v>
       </c>
-      <c r="C10" s="19" t="n">
+      <c r="C10" s="39" t="n">
         <f aca="false">C8*(1+C9)</f>
         <v>221837.6</v>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="26" t="n">
         <f aca="false">D8*(1+D9)</f>
         <v>194107.9</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="20" t="n">
+      <c r="A11" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" s="40" t="n">
         <f aca="false">B8-B10</f>
         <v>27729.7</v>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="40" t="n">
         <f aca="false">C8-C10</f>
         <v>55459.4</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="29" t="n">
         <f aca="false">D8-D10</f>
         <v>83189.1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" s="13" t="n">
+      <c r="A12" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="34" t="n">
         <f aca="false">B9-B11</f>
         <v>-27729.8</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="1" t="n">
+      <c r="A13" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="22" t="n">
         <f aca="false">WhatIf_Baseline!$B$2-WhatIf_Baseline!$B$3</f>
         <v>134187</v>
       </c>
-      <c r="C13" s="21" t="n">
+      <c r="C13" s="41" t="n">
         <f aca="false">WhatIf_Baseline!$B$2-WhatIf_Baseline!$B$3</f>
         <v>134187</v>
       </c>
-      <c r="D13" s="22" t="n">
+      <c r="D13" s="42" t="n">
         <f aca="false">WhatIf_Baseline!$B$2-WhatIf_Baseline!$B$3</f>
         <v>134187</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="23" t="n">
+      <c r="A14" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="43" t="n">
         <f aca="false">WhatIf_Input!C4</f>
         <v>0.1</v>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C14" s="38" t="n">
         <f aca="false">WhatIf_Input!D4</f>
         <v>0.1</v>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D14" s="32" t="n">
         <f aca="false">WhatIf_Input!E4</f>
         <v>0.1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="1" t="n">
+      <c r="A15" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" s="22" t="n">
         <f aca="false">B13*(1+B14)</f>
         <v>147605.7</v>
       </c>
-      <c r="C15" s="21" t="n">
+      <c r="C15" s="41" t="n">
         <f aca="false">C13*(1+C14)</f>
         <v>147605.7</v>
       </c>
-      <c r="D15" s="21" t="n">
+      <c r="D15" s="41" t="n">
         <f aca="false">D13*(1+D14)</f>
         <v>147605.7</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B16" s="1" t="n">
+      <c r="A16" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="22" t="n">
         <f aca="false">B15-B13</f>
         <v>13418.7</v>
       </c>
-      <c r="C16" s="21" t="n">
+      <c r="C16" s="41" t="n">
         <f aca="false">C15-C13</f>
         <v>13418.7</v>
       </c>
-      <c r="D16" s="21" t="n">
+      <c r="D16" s="41" t="n">
         <f aca="false">D15-D13</f>
         <v>13418.7</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
+      <c r="A17" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="1" t="n">
+      <c r="A18" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="22" t="n">
         <f aca="false">B5</f>
-        <v>3547094.88</v>
-      </c>
-      <c r="C18" s="21" t="n">
+        <v>3515399.6</v>
+      </c>
+      <c r="C18" s="41" t="n">
         <f aca="false">C5</f>
         <v>3651421.2</v>
       </c>
-      <c r="D18" s="21" t="n">
+      <c r="D18" s="41" t="n">
         <f aca="false">D5</f>
         <v>3825298.4</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B19" s="1" t="n">
+      <c r="A19" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" s="22" t="n">
         <f aca="false">B15</f>
         <v>147605.7</v>
       </c>
-      <c r="C19" s="21" t="n">
+      <c r="C19" s="41" t="n">
         <f aca="false">C15</f>
         <v>147605.7</v>
       </c>
-      <c r="D19" s="21" t="n">
+      <c r="D19" s="41" t="n">
         <f aca="false">D15</f>
         <v>147605.7</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="1" t="n">
+      <c r="A20" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="22" t="n">
         <f aca="false">B11</f>
         <v>27729.7</v>
       </c>
-      <c r="C20" s="21" t="n">
+      <c r="C20" s="41" t="n">
         <f aca="false">C11</f>
         <v>55459.4</v>
       </c>
-      <c r="D20" s="21" t="n">
+      <c r="D20" s="41" t="n">
         <f aca="false">D11</f>
         <v>83189.1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" s="1" t="n">
+      <c r="A21" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B21" s="22" t="n">
         <f aca="false">B18+B19+B20</f>
-        <v>3722430.28</v>
-      </c>
-      <c r="C21" s="21" t="n">
+        <v>3690735</v>
+      </c>
+      <c r="C21" s="41" t="n">
         <f aca="false">C18+C19+C20</f>
         <v>3854486.3</v>
       </c>
-      <c r="D21" s="21" t="n">
+      <c r="D21" s="41" t="n">
         <f aca="false">D18+D19+D20</f>
         <v>4056093.2</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B22" s="1" t="n">
+      <c r="A22" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22" s="22" t="n">
         <f aca="false">B21-WhatIf_Baseline!$B$2</f>
-        <v>110699.28</v>
-      </c>
-      <c r="C22" s="21" t="n">
+        <v>79004.0000000005</v>
+      </c>
+      <c r="C22" s="41" t="n">
         <f aca="false">C21-WhatIf_Baseline!$B$2</f>
         <v>242755.3</v>
       </c>
-      <c r="D22" s="21" t="n">
+      <c r="D22" s="41" t="n">
         <f aca="false">D21-WhatIf_Baseline!$B$2</f>
         <v>444362.200000001</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B23" s="24" t="n">
+      <c r="A23" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" s="44" t="n">
         <f aca="false">B22/WhatIf_Baseline!$B$2</f>
-        <v>0.030649923817693</v>
-      </c>
-      <c r="C23" s="25" t="n">
+        <v>0.0218742757973948</v>
+      </c>
+      <c r="C23" s="45" t="n">
         <f aca="false">C22/WhatIf_Baseline!$B$2</f>
         <v>0.0672130067272453</v>
       </c>
-      <c r="D23" s="25" t="n">
+      <c r="D23" s="45" t="n">
         <f aca="false">D22/WhatIf_Baseline!$B$2</f>
         <v>0.123033027653499</v>
       </c>
@@ -1277,4 +2512,76 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="12.84"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="46" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" s="5" t="n">
+        <f aca="false">WhatIf_Calculation!B21</f>
+        <v>3690735</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <f aca="false">WhatIf_Calculation!C21</f>
+        <v>3854486.3</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <f aca="false">WhatIf_Calculation!D21</f>
+        <v>4056093.2</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="47" t="n">
+        <f aca="false">WhatIf_Baseline!$B$2</f>
+        <v>3611731</v>
+      </c>
+      <c r="C3" s="47" t="n">
+        <f aca="false">WhatIf_Baseline!$B$2</f>
+        <v>3611731</v>
+      </c>
+      <c r="D3" s="47" t="n">
+        <f aca="false">WhatIf_Baseline!$B$2</f>
+        <v>3611731</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>